--- a/ragas_scores_by_llm.xlsx
+++ b/ragas_scores_by_llm.xlsx
@@ -439,7 +439,7 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>noise_sensitivity</t>
+          <t>noise_sensitivity(mode=relevant)</t>
         </is>
       </c>
     </row>
@@ -455,8 +455,12 @@
       <c r="C2" t="n">
         <v>0.2416</v>
       </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
+      <c r="D2" t="n">
+        <v>0.2455</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.0126</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
